--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -2570,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118386422</v>
+        <v>118388685</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,47 +2582,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509823</v>
+        <v>509659</v>
       </c>
       <c r="R19" t="n">
-        <v>6982819</v>
+        <v>6983042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2691,7 +2682,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118389865</v>
+        <v>118386422</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2726,7 +2717,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2736,14 +2727,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509614</v>
+        <v>509823</v>
       </c>
       <c r="R20" t="n">
-        <v>6983107</v>
+        <v>6982819</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2812,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118388685</v>
+        <v>118389865</v>
       </c>
       <c r="B21" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,38 +2815,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509659</v>
+        <v>509614</v>
       </c>
       <c r="R21" t="n">
-        <v>6983042</v>
+        <v>6983107</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118389674</v>
+        <v>118389872</v>
       </c>
       <c r="B35" t="n">
-        <v>97763</v>
+        <v>82263</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4457,25 +4457,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509557</v>
+        <v>509635</v>
       </c>
       <c r="R35" t="n">
-        <v>6983147</v>
+        <v>6983073</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4518,19 +4518,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4557,10 +4547,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118388520</v>
+        <v>118389674</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4569,47 +4559,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509627</v>
+        <v>509557</v>
       </c>
       <c r="R36" t="n">
-        <v>6983029</v>
+        <v>6983147</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4678,7 +4659,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118389380</v>
+        <v>118388520</v>
       </c>
       <c r="B37" t="n">
         <v>97846</v>
@@ -4713,7 +4694,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4727,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509533</v>
+        <v>509627</v>
       </c>
       <c r="R37" t="n">
-        <v>6983061</v>
+        <v>6983029</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4799,7 +4780,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118386476</v>
+        <v>118389380</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4834,7 +4815,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4844,14 +4825,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509827</v>
+        <v>509533</v>
       </c>
       <c r="R38" t="n">
-        <v>6982827</v>
+        <v>6983061</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4920,7 +4901,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118386834</v>
+        <v>118386476</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4955,7 +4936,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4969,10 +4950,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509731</v>
+        <v>509827</v>
       </c>
       <c r="R39" t="n">
-        <v>6982806</v>
+        <v>6982827</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5041,10 +5022,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118389872</v>
+        <v>118386834</v>
       </c>
       <c r="B40" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5053,41 +5034,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509635</v>
+        <v>509731</v>
       </c>
       <c r="R40" t="n">
-        <v>6983073</v>
+        <v>6982806</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5114,9 +5104,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118387158</v>
+        <v>118390002</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509666</v>
+        <v>509633</v>
       </c>
       <c r="R2" t="n">
-        <v>6982852</v>
+        <v>6983026</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118388690</v>
+        <v>118388830</v>
       </c>
       <c r="B3" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509589</v>
+        <v>509546</v>
       </c>
       <c r="R3" t="n">
-        <v>6982988</v>
+        <v>6982994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118389355</v>
+        <v>118388958</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -912,26 +931,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509527</v>
+        <v>509542</v>
       </c>
       <c r="R4" t="n">
-        <v>6983000</v>
+        <v>6982999</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1000,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118387503</v>
+        <v>118389927</v>
       </c>
       <c r="B5" t="n">
-        <v>95394</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1022,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509709</v>
+        <v>509647</v>
       </c>
       <c r="R5" t="n">
-        <v>6982882</v>
+        <v>6983063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1112,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118390002</v>
+        <v>118389789</v>
       </c>
       <c r="B6" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,41 +1143,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509633</v>
+        <v>509597</v>
       </c>
       <c r="R6" t="n">
-        <v>6983026</v>
+        <v>6983133</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,19 +1208,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118387192</v>
+        <v>118389609</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1259,27 +1272,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509740</v>
+        <v>509553</v>
       </c>
       <c r="R7" t="n">
-        <v>6982890</v>
+        <v>6983128</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,19 +1314,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118388205</v>
+        <v>118389031</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1380,7 +1378,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1394,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509638</v>
+        <v>509527</v>
       </c>
       <c r="R8" t="n">
-        <v>6983015</v>
+        <v>6983000</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1466,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118387551</v>
+        <v>118386422</v>
       </c>
       <c r="B9" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1476,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509687</v>
+        <v>509823</v>
       </c>
       <c r="R9" t="n">
-        <v>6982904</v>
+        <v>6982819</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,9 +1546,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118389079</v>
+        <v>118386834</v>
       </c>
       <c r="B10" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,41 +1597,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509510</v>
+        <v>509731</v>
       </c>
       <c r="R10" t="n">
-        <v>6982993</v>
+        <v>6982806</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,9 +1667,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118389356</v>
+        <v>118388301</v>
       </c>
       <c r="B11" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,42 +1718,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509532</v>
+        <v>509633</v>
       </c>
       <c r="R11" t="n">
-        <v>6983056</v>
+        <v>6982957</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118388830</v>
+        <v>118386731</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,50 +1829,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509546</v>
+        <v>509786</v>
       </c>
       <c r="R12" t="n">
-        <v>6982994</v>
+        <v>6982814</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,9 +1890,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118388857</v>
+        <v>118388685</v>
       </c>
       <c r="B13" t="n">
-        <v>96801</v>
+        <v>97867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509547</v>
+        <v>509659</v>
       </c>
       <c r="R13" t="n">
-        <v>6983031</v>
+        <v>6983042</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1999,7 +2041,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118390738</v>
+        <v>118389401</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2034,7 +2076,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2044,14 +2086,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509739</v>
+        <v>509534</v>
       </c>
       <c r="R14" t="n">
-        <v>6982916</v>
+        <v>6983061</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2120,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118386737</v>
+        <v>118387192</v>
       </c>
       <c r="B15" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,41 +2174,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509786</v>
+        <v>509740</v>
       </c>
       <c r="R15" t="n">
-        <v>6982789</v>
+        <v>6982890</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,9 +2244,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,7 +2283,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118389927</v>
+        <v>118389611</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2257,7 +2318,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2271,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509647</v>
+        <v>509572</v>
       </c>
       <c r="R16" t="n">
-        <v>6983063</v>
+        <v>6983118</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2343,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118388342</v>
+        <v>118390738</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2378,7 +2439,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2388,14 +2449,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509663</v>
+        <v>509739</v>
       </c>
       <c r="R17" t="n">
-        <v>6983023</v>
+        <v>6982916</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2464,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118389609</v>
+        <v>118386737</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,42 +2537,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509553</v>
+        <v>509786</v>
       </c>
       <c r="R18" t="n">
-        <v>6983128</v>
+        <v>6982789</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118388685</v>
+        <v>118389674</v>
       </c>
       <c r="B19" t="n">
-        <v>97867</v>
+        <v>97763</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,21 +2643,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509659</v>
+        <v>509557</v>
       </c>
       <c r="R19" t="n">
-        <v>6983042</v>
+        <v>6983147</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2682,7 +2739,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118386422</v>
+        <v>118388520</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2717,7 +2774,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2727,14 +2784,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509823</v>
+        <v>509627</v>
       </c>
       <c r="R20" t="n">
-        <v>6982819</v>
+        <v>6983029</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2803,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118389865</v>
+        <v>118388565</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2838,7 +2895,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2852,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509614</v>
+        <v>509621</v>
       </c>
       <c r="R21" t="n">
-        <v>6983107</v>
+        <v>6983031</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2924,7 +2981,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118388080</v>
+        <v>118386476</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -2959,7 +3016,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2973,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509631</v>
+        <v>509827</v>
       </c>
       <c r="R22" t="n">
-        <v>6982967</v>
+        <v>6982827</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3045,10 +3102,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118386731</v>
+        <v>118386677</v>
       </c>
       <c r="B23" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,25 +3114,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3142,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509786</v>
+        <v>509795</v>
       </c>
       <c r="R23" t="n">
-        <v>6982814</v>
+        <v>6982794</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3157,7 +3214,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118388802</v>
+        <v>118388316</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -3192,7 +3249,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3206,10 +3263,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509577</v>
+        <v>509638</v>
       </c>
       <c r="R24" t="n">
-        <v>6983044</v>
+        <v>6983022</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3278,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118387645</v>
+        <v>118388690</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3290,50 +3347,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509724</v>
+        <v>509589</v>
       </c>
       <c r="R25" t="n">
-        <v>6982889</v>
+        <v>6982988</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3360,19 +3408,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118388565</v>
+        <v>118388857</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,44 +3449,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509621</v>
+        <v>509547</v>
       </c>
       <c r="R26" t="n">
         <v>6983031</v>
@@ -3520,7 +3549,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118388600</v>
+        <v>118386659</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3555,7 +3584,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3565,14 +3594,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509628</v>
+        <v>509786</v>
       </c>
       <c r="R27" t="n">
-        <v>6983055</v>
+        <v>6982829</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3641,7 +3670,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118389611</v>
+        <v>118388342</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3676,7 +3705,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3690,10 +3719,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509572</v>
+        <v>509663</v>
       </c>
       <c r="R28" t="n">
-        <v>6983118</v>
+        <v>6983023</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3762,7 +3791,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118389789</v>
+        <v>118389865</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3797,7 +3826,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3806,13 +3840,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509597</v>
+        <v>509614</v>
       </c>
       <c r="R29" t="n">
-        <v>6983133</v>
+        <v>6983107</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3839,9 +3873,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3868,7 +3912,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118388958</v>
+        <v>118388205</v>
       </c>
       <c r="B30" t="n">
         <v>97846</v>
@@ -3901,17 +3945,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509542</v>
+        <v>509638</v>
       </c>
       <c r="R30" t="n">
-        <v>6982999</v>
+        <v>6983015</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3980,10 +4033,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118386677</v>
+        <v>118389872</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,41 +4045,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509795</v>
+        <v>509635</v>
       </c>
       <c r="R31" t="n">
-        <v>6982794</v>
+        <v>6983073</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,19 +4106,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,10 +4135,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118388316</v>
+        <v>118387158</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,50 +4147,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509638</v>
+        <v>509666</v>
       </c>
       <c r="R32" t="n">
-        <v>6983022</v>
+        <v>6982852</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,19 +4208,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4334,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118388526</v>
+        <v>118389356</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,47 +4370,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509630</v>
+        <v>509532</v>
       </c>
       <c r="R34" t="n">
-        <v>6982963</v>
+        <v>6983056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4445,7 +4464,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118389872</v>
+        <v>118387551</v>
       </c>
       <c r="B35" t="n">
         <v>82263</v>
@@ -4481,14 +4500,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509635</v>
+        <v>509687</v>
       </c>
       <c r="R35" t="n">
-        <v>6983073</v>
+        <v>6982904</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4547,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118389674</v>
+        <v>118388666</v>
       </c>
       <c r="B36" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4559,38 +4578,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509557</v>
+        <v>509650</v>
       </c>
       <c r="R36" t="n">
-        <v>6983147</v>
+        <v>6983040</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4659,7 +4687,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118388520</v>
+        <v>118387645</v>
       </c>
       <c r="B37" t="n">
         <v>97846</v>
@@ -4694,7 +4722,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4704,14 +4732,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509627</v>
+        <v>509724</v>
       </c>
       <c r="R37" t="n">
-        <v>6983029</v>
+        <v>6982889</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4780,7 +4808,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118389380</v>
+        <v>118389591</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4815,7 +4843,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4829,10 +4857,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509533</v>
+        <v>509579</v>
       </c>
       <c r="R38" t="n">
-        <v>6983061</v>
+        <v>6983105</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4901,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118386476</v>
+        <v>118389079</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4913,50 +4941,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509827</v>
+        <v>509510</v>
       </c>
       <c r="R39" t="n">
-        <v>6982827</v>
+        <v>6982993</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4983,19 +5002,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,10 +5031,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118386834</v>
+        <v>118387633</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5034,50 +5043,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509731</v>
+        <v>509689</v>
       </c>
       <c r="R40" t="n">
-        <v>6982806</v>
+        <v>6982906</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5104,19 +5104,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5143,7 +5133,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118388301</v>
+        <v>118389380</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -5178,27 +5168,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509633</v>
+        <v>509533</v>
       </c>
       <c r="R41" t="n">
-        <v>6982957</v>
+        <v>6983061</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5225,9 +5215,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,10 +5254,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118389591</v>
+        <v>118387503</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>95394</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5266,47 +5266,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509579</v>
+        <v>509709</v>
       </c>
       <c r="R42" t="n">
-        <v>6983105</v>
+        <v>6982882</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5375,7 +5366,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118389401</v>
+        <v>118388802</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5410,7 +5401,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5424,10 +5415,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509534</v>
+        <v>509577</v>
       </c>
       <c r="R43" t="n">
-        <v>6983061</v>
+        <v>6983044</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5496,7 +5487,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118386659</v>
+        <v>118388526</v>
       </c>
       <c r="B44" t="n">
         <v>97846</v>
@@ -5531,12 +5522,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5545,13 +5536,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509786</v>
+        <v>509630</v>
       </c>
       <c r="R44" t="n">
-        <v>6982829</v>
+        <v>6982963</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5578,19 +5569,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5738,10 +5719,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118387633</v>
+        <v>118388080</v>
       </c>
       <c r="B46" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5750,41 +5731,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509689</v>
+        <v>509631</v>
       </c>
       <c r="R46" t="n">
-        <v>6982906</v>
+        <v>6982967</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5811,9 +5801,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,7 +5840,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118388666</v>
+        <v>118388600</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509650</v>
+        <v>509628</v>
       </c>
       <c r="R47" t="n">
-        <v>6983040</v>
+        <v>6983055</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118765144</v>
+        <v>118766047</v>
       </c>
       <c r="B48" t="n">
         <v>97846</v>
@@ -5996,7 +5996,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509640</v>
+        <v>509608</v>
       </c>
       <c r="R48" t="n">
-        <v>6983034</v>
+        <v>6982971</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6040,7 +6045,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6050,7 +6055,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6077,7 +6082,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118766047</v>
+        <v>118765097</v>
       </c>
       <c r="B49" t="n">
         <v>97846</v>
@@ -6112,12 +6117,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>509608</v>
+        <v>509641</v>
       </c>
       <c r="R49" t="n">
-        <v>6982971</v>
+        <v>6983060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,10 +6198,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118765097</v>
+        <v>118765047</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,30 +6210,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>509641</v>
+        <v>509638</v>
       </c>
       <c r="R50" t="n">
-        <v>6983060</v>
+        <v>6983069</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765047</v>
+        <v>118765144</v>
       </c>
       <c r="B51" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,30 +6326,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509638</v>
+        <v>509640</v>
       </c>
       <c r="R51" t="n">
-        <v>6983069</v>
+        <v>6983034</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118389609</v>
+        <v>118386731</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,45 +1249,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509553</v>
+        <v>509786</v>
       </c>
       <c r="R7" t="n">
-        <v>6983128</v>
+        <v>6982814</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,9 +1310,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118389031</v>
+        <v>118389609</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1378,12 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1392,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509527</v>
+        <v>509553</v>
       </c>
       <c r="R8" t="n">
-        <v>6983000</v>
+        <v>6983128</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,19 +1426,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118386422</v>
+        <v>118389031</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1499,7 +1490,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1509,14 +1500,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509823</v>
+        <v>509527</v>
       </c>
       <c r="R9" t="n">
-        <v>6982819</v>
+        <v>6983000</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1585,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118386834</v>
+        <v>118386422</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1620,7 +1611,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1634,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509731</v>
+        <v>509823</v>
       </c>
       <c r="R10" t="n">
-        <v>6982806</v>
+        <v>6982819</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1706,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118388301</v>
+        <v>118386834</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1741,12 +1732,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,13 +1746,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509633</v>
+        <v>509731</v>
       </c>
       <c r="R11" t="n">
-        <v>6982957</v>
+        <v>6982806</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,9 +1779,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118386731</v>
+        <v>118388301</v>
       </c>
       <c r="B12" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,41 +1830,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509786</v>
+        <v>509633</v>
       </c>
       <c r="R12" t="n">
-        <v>6982814</v>
+        <v>6982957</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,19 +1900,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118389356</v>
+        <v>118387551</v>
       </c>
       <c r="B34" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,42 +4370,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509532</v>
+        <v>509687</v>
       </c>
       <c r="R34" t="n">
-        <v>6983056</v>
+        <v>6982904</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4464,10 +4460,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118387551</v>
+        <v>118388666</v>
       </c>
       <c r="B35" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4476,41 +4472,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509687</v>
+        <v>509650</v>
       </c>
       <c r="R35" t="n">
-        <v>6982904</v>
+        <v>6983040</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4537,9 +4542,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4581,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118388666</v>
+        <v>118389356</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4578,35 +4593,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4615,13 +4625,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509650</v>
+        <v>509532</v>
       </c>
       <c r="R36" t="n">
-        <v>6983040</v>
+        <v>6983056</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4648,19 +4658,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4687,10 +4687,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118387645</v>
+        <v>118389079</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4699,50 +4699,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509724</v>
+        <v>509510</v>
       </c>
       <c r="R37" t="n">
-        <v>6982889</v>
+        <v>6982993</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4769,19 +4760,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,7 +4789,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118389591</v>
+        <v>118387645</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4843,7 +4824,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4853,14 +4834,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509579</v>
+        <v>509724</v>
       </c>
       <c r="R38" t="n">
-        <v>6983105</v>
+        <v>6982889</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4929,10 +4910,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118389079</v>
+        <v>118389591</v>
       </c>
       <c r="B39" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4941,41 +4922,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509510</v>
+        <v>509579</v>
       </c>
       <c r="R39" t="n">
-        <v>6982993</v>
+        <v>6983105</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5002,9 +4992,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118390002</v>
+        <v>118387633</v>
       </c>
       <c r="B2" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509633</v>
+        <v>509689</v>
       </c>
       <c r="R2" t="n">
-        <v>6983026</v>
+        <v>6982906</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118388830</v>
+        <v>118389401</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -822,12 +812,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509546</v>
+        <v>509534</v>
       </c>
       <c r="R3" t="n">
-        <v>6982994</v>
+        <v>6983061</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,9 +859,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118388958</v>
+        <v>118389748</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -931,17 +931,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509542</v>
+        <v>509598</v>
       </c>
       <c r="R4" t="n">
-        <v>6982999</v>
+        <v>6983133</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1010,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118389927</v>
+        <v>118388205</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1045,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1059,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509647</v>
+        <v>509638</v>
       </c>
       <c r="R5" t="n">
-        <v>6983063</v>
+        <v>6983015</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1131,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118389789</v>
+        <v>118387192</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1166,22 +1175,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509597</v>
+        <v>509740</v>
       </c>
       <c r="R6" t="n">
-        <v>6983133</v>
+        <v>6982890</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1222,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118386731</v>
+        <v>118388666</v>
       </c>
       <c r="B7" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,38 +1273,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509786</v>
+        <v>509650</v>
       </c>
       <c r="R7" t="n">
-        <v>6982814</v>
+        <v>6983040</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118389609</v>
+        <v>118388520</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1384,7 +1417,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1393,13 +1431,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509553</v>
+        <v>509627</v>
       </c>
       <c r="R8" t="n">
-        <v>6983128</v>
+        <v>6983029</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,9 +1464,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,7 +1503,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118389031</v>
+        <v>118388301</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1490,27 +1538,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509527</v>
+        <v>509633</v>
       </c>
       <c r="R9" t="n">
-        <v>6983000</v>
+        <v>6982957</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,19 +1585,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118386422</v>
+        <v>118387421</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1611,7 +1649,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509823</v>
+        <v>509760</v>
       </c>
       <c r="R10" t="n">
-        <v>6982819</v>
+        <v>6982916</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1697,7 +1735,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118386834</v>
+        <v>118388080</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1732,7 +1770,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1746,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509731</v>
+        <v>509631</v>
       </c>
       <c r="R11" t="n">
-        <v>6982806</v>
+        <v>6982967</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1818,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118388301</v>
+        <v>118389356</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,47 +1868,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509633</v>
+        <v>509532</v>
       </c>
       <c r="R12" t="n">
-        <v>6982957</v>
+        <v>6983056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118388685</v>
+        <v>118386737</v>
       </c>
       <c r="B13" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,41 +1974,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509659</v>
+        <v>509786</v>
       </c>
       <c r="R13" t="n">
-        <v>6983042</v>
+        <v>6982789</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2002,19 +2035,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2064,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118389401</v>
+        <v>118388802</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2076,7 +2099,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2090,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509534</v>
+        <v>509577</v>
       </c>
       <c r="R14" t="n">
-        <v>6983061</v>
+        <v>6983044</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2162,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118387192</v>
+        <v>118389031</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2197,7 +2220,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2207,14 +2230,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509740</v>
+        <v>509527</v>
       </c>
       <c r="R15" t="n">
-        <v>6982890</v>
+        <v>6983000</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2283,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118389611</v>
+        <v>118388565</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2318,7 +2341,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2332,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509572</v>
+        <v>509621</v>
       </c>
       <c r="R16" t="n">
-        <v>6983118</v>
+        <v>6983031</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2404,7 +2427,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118390738</v>
+        <v>118388830</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2439,27 +2462,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509739</v>
+        <v>509546</v>
       </c>
       <c r="R17" t="n">
-        <v>6982916</v>
+        <v>6982994</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,19 +2509,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118386737</v>
+        <v>118389865</v>
       </c>
       <c r="B18" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,41 +2550,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509786</v>
+        <v>509614</v>
       </c>
       <c r="R18" t="n">
-        <v>6982789</v>
+        <v>6983107</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,9 +2620,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118389674</v>
+        <v>118389611</v>
       </c>
       <c r="B19" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,38 +2671,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509557</v>
+        <v>509572</v>
       </c>
       <c r="R19" t="n">
-        <v>6983147</v>
+        <v>6983118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2739,7 +2780,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118388520</v>
+        <v>118386422</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2774,7 +2815,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2784,14 +2825,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509627</v>
+        <v>509823</v>
       </c>
       <c r="R20" t="n">
-        <v>6983029</v>
+        <v>6982819</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2860,7 +2901,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118388565</v>
+        <v>118386677</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2893,26 +2934,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509621</v>
+        <v>509795</v>
       </c>
       <c r="R21" t="n">
-        <v>6983031</v>
+        <v>6982794</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2981,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118386476</v>
+        <v>118388857</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,47 +3025,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509827</v>
+        <v>509547</v>
       </c>
       <c r="R22" t="n">
-        <v>6982827</v>
+        <v>6983031</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3102,7 +3125,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118386677</v>
+        <v>118390738</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3135,17 +3158,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509795</v>
+        <v>509739</v>
       </c>
       <c r="R23" t="n">
-        <v>6982794</v>
+        <v>6982916</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3214,7 +3246,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118388316</v>
+        <v>118389789</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -3249,12 +3281,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>103</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3263,13 +3290,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509638</v>
+        <v>509597</v>
       </c>
       <c r="R24" t="n">
-        <v>6983022</v>
+        <v>6983133</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3296,19 +3323,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,10 +3352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118388690</v>
+        <v>118389609</v>
       </c>
       <c r="B25" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3347,38 +3364,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509589</v>
+        <v>509553</v>
       </c>
       <c r="R25" t="n">
-        <v>6982988</v>
+        <v>6983128</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3437,10 +3458,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118388857</v>
+        <v>118388600</v>
       </c>
       <c r="B26" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,38 +3470,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509547</v>
+        <v>509628</v>
       </c>
       <c r="R26" t="n">
-        <v>6983031</v>
+        <v>6983055</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3549,7 +3579,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118386659</v>
+        <v>118386476</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3584,7 +3614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3598,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509786</v>
+        <v>509827</v>
       </c>
       <c r="R27" t="n">
-        <v>6982829</v>
+        <v>6982827</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3670,10 +3700,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118388342</v>
+        <v>118387158</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3682,50 +3712,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509663</v>
+        <v>509666</v>
       </c>
       <c r="R28" t="n">
-        <v>6983023</v>
+        <v>6982852</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,19 +3773,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,7 +3802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118389865</v>
+        <v>118388316</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3826,7 +3837,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3840,10 +3851,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509614</v>
+        <v>509638</v>
       </c>
       <c r="R29" t="n">
-        <v>6983107</v>
+        <v>6983022</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3912,10 +3923,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118388205</v>
+        <v>118390002</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3924,47 +3935,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509638</v>
+        <v>509633</v>
       </c>
       <c r="R30" t="n">
-        <v>6983015</v>
+        <v>6983026</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4033,10 +4035,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118389872</v>
+        <v>118386659</v>
       </c>
       <c r="B31" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4045,41 +4047,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509635</v>
+        <v>509786</v>
       </c>
       <c r="R31" t="n">
-        <v>6983073</v>
+        <v>6982829</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4106,9 +4117,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4135,10 +4156,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118387158</v>
+        <v>118389079</v>
       </c>
       <c r="B32" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4151,34 +4172,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509666</v>
+        <v>509510</v>
       </c>
       <c r="R32" t="n">
-        <v>6982852</v>
+        <v>6982993</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4237,10 +4258,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118387421</v>
+        <v>118389674</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4249,47 +4270,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509760</v>
+        <v>509557</v>
       </c>
       <c r="R33" t="n">
-        <v>6982916</v>
+        <v>6983147</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4358,10 +4370,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118387551</v>
+        <v>118387503</v>
       </c>
       <c r="B34" t="n">
-        <v>82263</v>
+        <v>95394</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4374,21 +4386,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4398,13 +4410,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509687</v>
+        <v>509709</v>
       </c>
       <c r="R34" t="n">
-        <v>6982904</v>
+        <v>6982882</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4431,9 +4443,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,7 +4482,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118388666</v>
+        <v>118388342</v>
       </c>
       <c r="B35" t="n">
         <v>97846</v>
@@ -4495,7 +4517,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4509,10 +4531,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509650</v>
+        <v>509663</v>
       </c>
       <c r="R35" t="n">
-        <v>6983040</v>
+        <v>6983023</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4581,10 +4603,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118389356</v>
+        <v>118389872</v>
       </c>
       <c r="B36" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4593,42 +4615,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509532</v>
+        <v>509635</v>
       </c>
       <c r="R36" t="n">
-        <v>6983056</v>
+        <v>6983073</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4687,10 +4705,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118389079</v>
+        <v>118388690</v>
       </c>
       <c r="B37" t="n">
-        <v>90788</v>
+        <v>90524</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4703,21 +4721,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4727,10 +4745,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509510</v>
+        <v>509589</v>
       </c>
       <c r="R37" t="n">
-        <v>6982993</v>
+        <v>6982988</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4789,7 +4807,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118387645</v>
+        <v>118389591</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4824,7 +4842,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4834,14 +4852,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509724</v>
+        <v>509579</v>
       </c>
       <c r="R38" t="n">
-        <v>6982889</v>
+        <v>6983105</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4910,7 +4928,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118389591</v>
+        <v>118387645</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4945,7 +4963,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4955,14 +4973,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509579</v>
+        <v>509724</v>
       </c>
       <c r="R39" t="n">
-        <v>6983105</v>
+        <v>6982889</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5031,10 +5049,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118387633</v>
+        <v>118386731</v>
       </c>
       <c r="B40" t="n">
-        <v>82263</v>
+        <v>104940</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5043,25 +5061,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5071,13 +5089,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509689</v>
+        <v>509786</v>
       </c>
       <c r="R40" t="n">
-        <v>6982906</v>
+        <v>6982814</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5104,9 +5122,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5133,7 +5161,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118389380</v>
+        <v>118386834</v>
       </c>
       <c r="B41" t="n">
         <v>97846</v>
@@ -5168,7 +5196,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5178,14 +5206,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509533</v>
+        <v>509731</v>
       </c>
       <c r="R41" t="n">
-        <v>6983061</v>
+        <v>6982806</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5254,10 +5282,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118387503</v>
+        <v>118389380</v>
       </c>
       <c r="B42" t="n">
-        <v>95394</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5266,38 +5294,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509709</v>
+        <v>509533</v>
       </c>
       <c r="R42" t="n">
-        <v>6982882</v>
+        <v>6983061</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5366,7 +5403,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118388802</v>
+        <v>118389927</v>
       </c>
       <c r="B43" t="n">
         <v>97846</v>
@@ -5401,7 +5438,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5415,10 +5452,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509577</v>
+        <v>509647</v>
       </c>
       <c r="R43" t="n">
-        <v>6983044</v>
+        <v>6983063</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5487,10 +5524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118388526</v>
+        <v>118388685</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5499,50 +5536,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509630</v>
+        <v>509659</v>
       </c>
       <c r="R44" t="n">
-        <v>6982963</v>
+        <v>6983042</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5569,9 +5597,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5598,10 +5636,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118389748</v>
+        <v>118387551</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,50 +5648,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509598</v>
+        <v>509687</v>
       </c>
       <c r="R45" t="n">
-        <v>6983133</v>
+        <v>6982904</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5680,19 +5709,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5719,7 +5738,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118388080</v>
+        <v>118388526</v>
       </c>
       <c r="B46" t="n">
         <v>97846</v>
@@ -5754,12 +5773,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5768,13 +5787,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509631</v>
+        <v>509630</v>
       </c>
       <c r="R46" t="n">
-        <v>6982967</v>
+        <v>6982963</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5801,19 +5820,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,7 +5849,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118388600</v>
+        <v>118388958</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5873,26 +5882,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509628</v>
+        <v>509542</v>
       </c>
       <c r="R47" t="n">
-        <v>6983055</v>
+        <v>6982999</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118766047</v>
+        <v>118765144</v>
       </c>
       <c r="B48" t="n">
         <v>97846</v>
@@ -5996,12 +5996,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6010,10 +6005,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509608</v>
+        <v>509640</v>
       </c>
       <c r="R48" t="n">
-        <v>6982971</v>
+        <v>6983034</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6045,7 +6040,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6055,7 +6050,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,7 +6077,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118765097</v>
+        <v>118766047</v>
       </c>
       <c r="B49" t="n">
         <v>97846</v>
@@ -6117,7 +6112,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>509641</v>
+        <v>509608</v>
       </c>
       <c r="R49" t="n">
-        <v>6983060</v>
+        <v>6982971</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,10 +6198,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118765047</v>
+        <v>118765097</v>
       </c>
       <c r="B50" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,30 +6210,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>509638</v>
+        <v>509641</v>
       </c>
       <c r="R50" t="n">
-        <v>6983069</v>
+        <v>6983060</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765144</v>
+        <v>118765047</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,30 +6326,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509640</v>
+        <v>509638</v>
       </c>
       <c r="R51" t="n">
-        <v>6983034</v>
+        <v>6983069</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118387633</v>
+        <v>118387158</v>
       </c>
       <c r="B2" t="n">
-        <v>82263</v>
+        <v>90511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509689</v>
+        <v>509666</v>
       </c>
       <c r="R2" t="n">
-        <v>6982906</v>
+        <v>6982852</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118389401</v>
+        <v>118387503</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>95401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509534</v>
+        <v>509709</v>
       </c>
       <c r="R3" t="n">
-        <v>6983061</v>
+        <v>6982882</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118389748</v>
+        <v>118388958</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +922,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509598</v>
+        <v>509542</v>
       </c>
       <c r="R4" t="n">
-        <v>6983133</v>
+        <v>6982999</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1019,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118388205</v>
+        <v>118389927</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509638</v>
+        <v>509647</v>
       </c>
       <c r="R5" t="n">
-        <v>6983015</v>
+        <v>6983063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1140,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118387192</v>
+        <v>118389674</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,47 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509740</v>
+        <v>509557</v>
       </c>
       <c r="R6" t="n">
-        <v>6982890</v>
+        <v>6983147</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1261,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118388666</v>
+        <v>118389401</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,7 +1269,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1310,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509650</v>
+        <v>509534</v>
       </c>
       <c r="R7" t="n">
-        <v>6983040</v>
+        <v>6983061</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1382,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118388520</v>
+        <v>118386476</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,7 +1390,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1427,14 +1400,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509627</v>
+        <v>509827</v>
       </c>
       <c r="R8" t="n">
-        <v>6983029</v>
+        <v>6982827</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1503,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118388301</v>
+        <v>118389748</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,27 +1511,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509633</v>
+        <v>509598</v>
       </c>
       <c r="R9" t="n">
-        <v>6982957</v>
+        <v>6983133</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,9 +1558,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118387421</v>
+        <v>118389865</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,14 +1642,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509760</v>
+        <v>509614</v>
       </c>
       <c r="R10" t="n">
-        <v>6982916</v>
+        <v>6983107</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1735,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118388080</v>
+        <v>118389355</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,7 +1753,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1780,14 +1763,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509631</v>
+        <v>509527</v>
       </c>
       <c r="R11" t="n">
-        <v>6982967</v>
+        <v>6983000</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1856,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118389356</v>
+        <v>118387421</v>
       </c>
       <c r="B12" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,45 +1851,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509532</v>
+        <v>509760</v>
       </c>
       <c r="R12" t="n">
-        <v>6983056</v>
+        <v>6982916</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,9 +1921,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118386737</v>
+        <v>118388857</v>
       </c>
       <c r="B13" t="n">
-        <v>82263</v>
+        <v>96808</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,41 +1972,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509786</v>
+        <v>509547</v>
       </c>
       <c r="R13" t="n">
-        <v>6982789</v>
+        <v>6983031</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2035,9 +2033,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118388802</v>
+        <v>118388526</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,27 +2107,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509577</v>
+        <v>509630</v>
       </c>
       <c r="R14" t="n">
-        <v>6983044</v>
+        <v>6982963</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,19 +2154,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118389031</v>
+        <v>118389079</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90795</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,50 +2195,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509527</v>
+        <v>509510</v>
       </c>
       <c r="R15" t="n">
-        <v>6983000</v>
+        <v>6982993</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,19 +2256,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118388565</v>
+        <v>118389609</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,12 +2320,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2355,13 +2329,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509621</v>
+        <v>509553</v>
       </c>
       <c r="R16" t="n">
-        <v>6983031</v>
+        <v>6983128</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,19 +2362,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,10 +2391,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118388830</v>
+        <v>118386731</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,50 +2403,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509546</v>
+        <v>509786</v>
       </c>
       <c r="R17" t="n">
-        <v>6982994</v>
+        <v>6982814</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2509,9 +2464,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118389865</v>
+        <v>118388685</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,47 +2515,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509614</v>
+        <v>509659</v>
       </c>
       <c r="R18" t="n">
-        <v>6983107</v>
+        <v>6983042</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2659,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118389611</v>
+        <v>118386737</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,50 +2627,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509572</v>
+        <v>509786</v>
       </c>
       <c r="R19" t="n">
-        <v>6983118</v>
+        <v>6982789</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2741,19 +2688,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118386422</v>
+        <v>118387551</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2792,50 +2729,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509823</v>
+        <v>509687</v>
       </c>
       <c r="R20" t="n">
-        <v>6982819</v>
+        <v>6982904</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2862,19 +2790,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,10 +2819,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118386677</v>
+        <v>118388520</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2934,17 +2852,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509795</v>
+        <v>509627</v>
       </c>
       <c r="R21" t="n">
-        <v>6982794</v>
+        <v>6983029</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3013,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118388857</v>
+        <v>118389789</v>
       </c>
       <c r="B22" t="n">
-        <v>96801</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,41 +2952,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509547</v>
+        <v>509597</v>
       </c>
       <c r="R22" t="n">
-        <v>6983031</v>
+        <v>6983133</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3086,19 +3017,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118390738</v>
+        <v>118388205</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,7 +3081,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3170,14 +3091,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509739</v>
+        <v>509638</v>
       </c>
       <c r="R23" t="n">
-        <v>6982916</v>
+        <v>6983015</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3246,10 +3167,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118389789</v>
+        <v>118388666</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,7 +3202,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3290,13 +3216,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509597</v>
+        <v>509650</v>
       </c>
       <c r="R24" t="n">
-        <v>6983133</v>
+        <v>6983040</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3323,9 +3249,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,10 +3288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118389609</v>
+        <v>118389872</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3364,42 +3300,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509553</v>
+        <v>509635</v>
       </c>
       <c r="R25" t="n">
-        <v>6983128</v>
+        <v>6983073</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3458,10 +3390,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118388600</v>
+        <v>118388690</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3470,50 +3402,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509628</v>
+        <v>509589</v>
       </c>
       <c r="R26" t="n">
-        <v>6983055</v>
+        <v>6982988</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3540,19 +3463,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,10 +3492,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118386476</v>
+        <v>118390738</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3614,7 +3527,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3628,10 +3541,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509827</v>
+        <v>509739</v>
       </c>
       <c r="R27" t="n">
-        <v>6982827</v>
+        <v>6982916</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3700,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118387158</v>
+        <v>118388316</v>
       </c>
       <c r="B28" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3712,41 +3625,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509666</v>
+        <v>509638</v>
       </c>
       <c r="R28" t="n">
-        <v>6982852</v>
+        <v>6983022</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3773,9 +3695,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3802,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118388316</v>
+        <v>118388830</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3837,12 +3769,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3851,13 +3783,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509638</v>
+        <v>509546</v>
       </c>
       <c r="R29" t="n">
-        <v>6983022</v>
+        <v>6982994</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3884,19 +3816,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,10 +3845,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118390002</v>
+        <v>118389380</v>
       </c>
       <c r="B30" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,38 +3857,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509633</v>
+        <v>509533</v>
       </c>
       <c r="R30" t="n">
-        <v>6983026</v>
+        <v>6983061</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4035,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118386659</v>
+        <v>118388342</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4070,7 +4001,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4080,14 +4011,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509786</v>
+        <v>509663</v>
       </c>
       <c r="R31" t="n">
-        <v>6982829</v>
+        <v>6983023</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4156,10 +4087,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118389079</v>
+        <v>118386422</v>
       </c>
       <c r="B32" t="n">
-        <v>90788</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4168,41 +4099,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509510</v>
+        <v>509823</v>
       </c>
       <c r="R32" t="n">
-        <v>6982993</v>
+        <v>6982819</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4229,9 +4169,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4258,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118389674</v>
+        <v>118386834</v>
       </c>
       <c r="B33" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4270,38 +4220,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509557</v>
+        <v>509731</v>
       </c>
       <c r="R33" t="n">
-        <v>6983147</v>
+        <v>6982806</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4370,10 +4329,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118387503</v>
+        <v>118387192</v>
       </c>
       <c r="B34" t="n">
-        <v>95394</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4382,38 +4341,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509709</v>
+        <v>509740</v>
       </c>
       <c r="R34" t="n">
-        <v>6982882</v>
+        <v>6982890</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4482,10 +4450,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118388342</v>
+        <v>118388080</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4517,7 +4485,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4527,14 +4495,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509663</v>
+        <v>509631</v>
       </c>
       <c r="R35" t="n">
-        <v>6983023</v>
+        <v>6982967</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4603,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118389872</v>
+        <v>118388301</v>
       </c>
       <c r="B36" t="n">
-        <v>82263</v>
+        <v>97853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4615,38 +4583,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509635</v>
+        <v>509633</v>
       </c>
       <c r="R36" t="n">
-        <v>6983073</v>
+        <v>6982957</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4705,10 +4682,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118388690</v>
+        <v>118389591</v>
       </c>
       <c r="B37" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4717,41 +4694,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509589</v>
+        <v>509579</v>
       </c>
       <c r="R37" t="n">
-        <v>6982988</v>
+        <v>6983105</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4778,9 +4764,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4807,10 +4803,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118389591</v>
+        <v>118390002</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4819,47 +4815,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509579</v>
+        <v>509633</v>
       </c>
       <c r="R38" t="n">
-        <v>6983105</v>
+        <v>6983026</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4928,10 +4915,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118387645</v>
+        <v>118388600</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4963,7 +4950,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4973,14 +4960,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509724</v>
+        <v>509628</v>
       </c>
       <c r="R39" t="n">
-        <v>6982889</v>
+        <v>6983055</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5049,10 +5036,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118386731</v>
+        <v>118386677</v>
       </c>
       <c r="B40" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,25 +5048,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5076,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509786</v>
+        <v>509795</v>
       </c>
       <c r="R40" t="n">
-        <v>6982814</v>
+        <v>6982794</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5161,10 +5148,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118386834</v>
+        <v>118386659</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5196,7 +5183,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5210,10 +5197,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509731</v>
+        <v>509786</v>
       </c>
       <c r="R41" t="n">
-        <v>6982806</v>
+        <v>6982829</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5282,10 +5269,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118389380</v>
+        <v>118388565</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,7 +5304,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5331,10 +5318,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509533</v>
+        <v>509621</v>
       </c>
       <c r="R42" t="n">
-        <v>6983061</v>
+        <v>6983031</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5403,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118389927</v>
+        <v>118387633</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5415,50 +5402,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509647</v>
+        <v>509689</v>
       </c>
       <c r="R43" t="n">
-        <v>6983063</v>
+        <v>6982906</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5485,19 +5463,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5524,10 +5492,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118388685</v>
+        <v>118387645</v>
       </c>
       <c r="B44" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5536,38 +5504,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509659</v>
+        <v>509724</v>
       </c>
       <c r="R44" t="n">
-        <v>6983042</v>
+        <v>6982889</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5636,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118387551</v>
+        <v>118389356</v>
       </c>
       <c r="B45" t="n">
-        <v>82263</v>
+        <v>97874</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5648,38 +5625,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509687</v>
+        <v>509532</v>
       </c>
       <c r="R45" t="n">
-        <v>6982904</v>
+        <v>6983056</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5738,10 +5719,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118388526</v>
+        <v>118389611</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5773,27 +5754,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509630</v>
+        <v>509572</v>
       </c>
       <c r="R46" t="n">
-        <v>6982963</v>
+        <v>6983118</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5820,9 +5801,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5849,10 +5840,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118388958</v>
+        <v>118388802</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,17 +5873,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509542</v>
+        <v>509577</v>
       </c>
       <c r="R47" t="n">
-        <v>6982999</v>
+        <v>6983044</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5964,7 +5964,7 @@
         <v>118765144</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>118766047</v>
       </c>
       <c r="B49" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118765097</v>
+        <v>118765047</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,30 +6210,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>509641</v>
+        <v>509638</v>
       </c>
       <c r="R50" t="n">
-        <v>6983060</v>
+        <v>6983069</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765047</v>
+        <v>118765097</v>
       </c>
       <c r="B51" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,30 +6326,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509638</v>
+        <v>509641</v>
       </c>
       <c r="R51" t="n">
-        <v>6983069</v>
+        <v>6983060</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -5148,10 +5148,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118386659</v>
+        <v>118387633</v>
       </c>
       <c r="B41" t="n">
-        <v>97853</v>
+        <v>82270</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5160,50 +5160,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509786</v>
+        <v>509689</v>
       </c>
       <c r="R41" t="n">
-        <v>6982829</v>
+        <v>6982906</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5230,19 +5221,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5269,7 +5250,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118388565</v>
+        <v>118386659</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -5304,7 +5285,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5314,14 +5295,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509621</v>
+        <v>509786</v>
       </c>
       <c r="R42" t="n">
-        <v>6983031</v>
+        <v>6982829</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5390,10 +5371,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118387633</v>
+        <v>118388565</v>
       </c>
       <c r="B43" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,41 +5383,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509689</v>
+        <v>509621</v>
       </c>
       <c r="R43" t="n">
-        <v>6982906</v>
+        <v>6983031</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5463,9 +5453,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118387158</v>
+        <v>118388080</v>
       </c>
       <c r="B2" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509666</v>
+        <v>509631</v>
       </c>
       <c r="R2" t="n">
-        <v>6982852</v>
+        <v>6982967</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +757,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118387503</v>
+        <v>118388802</v>
       </c>
       <c r="B3" t="n">
-        <v>95401</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509709</v>
+        <v>509577</v>
       </c>
       <c r="R3" t="n">
-        <v>6982882</v>
+        <v>6983044</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118388958</v>
+        <v>118387158</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +929,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509542</v>
+        <v>509666</v>
       </c>
       <c r="R4" t="n">
-        <v>6982999</v>
+        <v>6982852</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,19 +990,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118389927</v>
+        <v>118389380</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1036,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1050,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509647</v>
+        <v>509533</v>
       </c>
       <c r="R5" t="n">
-        <v>6983063</v>
+        <v>6983061</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1122,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118389674</v>
+        <v>118389927</v>
       </c>
       <c r="B6" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1152,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509557</v>
+        <v>509647</v>
       </c>
       <c r="R6" t="n">
-        <v>6983147</v>
+        <v>6983063</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118389401</v>
+        <v>118387503</v>
       </c>
       <c r="B7" t="n">
-        <v>97853</v>
+        <v>95401</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,47 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509534</v>
+        <v>509709</v>
       </c>
       <c r="R7" t="n">
-        <v>6983061</v>
+        <v>6982882</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,7 +1373,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118386476</v>
+        <v>118389748</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1390,7 +1408,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1400,14 +1418,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509827</v>
+        <v>509598</v>
       </c>
       <c r="R8" t="n">
-        <v>6982827</v>
+        <v>6983133</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1476,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118389748</v>
+        <v>118388316</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1511,7 +1529,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1525,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509598</v>
+        <v>509638</v>
       </c>
       <c r="R9" t="n">
-        <v>6983133</v>
+        <v>6983022</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1597,7 +1615,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118389865</v>
+        <v>118389591</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1632,7 +1650,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1646,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509614</v>
+        <v>509579</v>
       </c>
       <c r="R10" t="n">
-        <v>6983107</v>
+        <v>6983105</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1718,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118389355</v>
+        <v>118386737</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>82270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,50 +1748,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509527</v>
+        <v>509786</v>
       </c>
       <c r="R11" t="n">
-        <v>6983000</v>
+        <v>6982789</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,19 +1809,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,7 +1838,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118387421</v>
+        <v>118386422</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1874,7 +1873,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1888,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509760</v>
+        <v>509823</v>
       </c>
       <c r="R12" t="n">
-        <v>6982916</v>
+        <v>6982819</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1960,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118388857</v>
+        <v>118389674</v>
       </c>
       <c r="B13" t="n">
-        <v>96808</v>
+        <v>97770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,21 +1975,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2000,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509547</v>
+        <v>509557</v>
       </c>
       <c r="R13" t="n">
-        <v>6983031</v>
+        <v>6983147</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2072,7 +2071,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118388526</v>
+        <v>118388565</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2107,27 +2106,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509630</v>
+        <v>509621</v>
       </c>
       <c r="R14" t="n">
-        <v>6982963</v>
+        <v>6983031</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,9 +2153,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118389079</v>
+        <v>118388301</v>
       </c>
       <c r="B15" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,38 +2204,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509510</v>
+        <v>509633</v>
       </c>
       <c r="R15" t="n">
-        <v>6982993</v>
+        <v>6982957</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2303,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118389609</v>
+        <v>118386476</v>
       </c>
       <c r="B16" t="n">
         <v>97853</v>
@@ -2320,22 +2338,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509553</v>
+        <v>509827</v>
       </c>
       <c r="R16" t="n">
-        <v>6983128</v>
+        <v>6982827</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,9 +2385,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118386731</v>
+        <v>118390002</v>
       </c>
       <c r="B17" t="n">
-        <v>104947</v>
+        <v>97874</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,34 +2440,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509786</v>
+        <v>509633</v>
       </c>
       <c r="R17" t="n">
-        <v>6982814</v>
+        <v>6983026</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2503,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118388685</v>
+        <v>118388857</v>
       </c>
       <c r="B18" t="n">
-        <v>97874</v>
+        <v>96808</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,21 +2552,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2543,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509659</v>
+        <v>509547</v>
       </c>
       <c r="R18" t="n">
-        <v>6983042</v>
+        <v>6983031</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2615,7 +2648,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118386737</v>
+        <v>118387633</v>
       </c>
       <c r="B19" t="n">
         <v>82270</v>
@@ -2655,10 +2688,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509786</v>
+        <v>509689</v>
       </c>
       <c r="R19" t="n">
-        <v>6982789</v>
+        <v>6982906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2717,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118387551</v>
+        <v>118386659</v>
       </c>
       <c r="B20" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,41 +2762,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509687</v>
+        <v>509786</v>
       </c>
       <c r="R20" t="n">
-        <v>6982904</v>
+        <v>6982829</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2790,9 +2832,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,7 +2992,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118389789</v>
+        <v>118388342</v>
       </c>
       <c r="B22" t="n">
         <v>97853</v>
@@ -2975,7 +3027,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2984,13 +3041,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509597</v>
+        <v>509663</v>
       </c>
       <c r="R22" t="n">
-        <v>6983133</v>
+        <v>6983023</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,9 +3074,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,10 +3113,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118388205</v>
+        <v>118389079</v>
       </c>
       <c r="B23" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,50 +3125,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509638</v>
+        <v>509510</v>
       </c>
       <c r="R23" t="n">
-        <v>6983015</v>
+        <v>6982993</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3128,19 +3186,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3167,7 +3215,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118388666</v>
+        <v>118387192</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3202,7 +3250,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3212,14 +3260,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509650</v>
+        <v>509740</v>
       </c>
       <c r="R24" t="n">
-        <v>6983040</v>
+        <v>6982890</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3288,7 +3336,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118389872</v>
+        <v>118387551</v>
       </c>
       <c r="B25" t="n">
         <v>82270</v>
@@ -3324,14 +3372,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509635</v>
+        <v>509687</v>
       </c>
       <c r="R25" t="n">
-        <v>6983073</v>
+        <v>6982904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3390,10 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118388690</v>
+        <v>118389401</v>
       </c>
       <c r="B26" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3402,41 +3450,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509589</v>
+        <v>509534</v>
       </c>
       <c r="R26" t="n">
-        <v>6982988</v>
+        <v>6983061</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3463,9 +3520,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3613,7 +3680,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118388316</v>
+        <v>118389355</v>
       </c>
       <c r="B28" t="n">
         <v>97853</v>
@@ -3648,7 +3715,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3662,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509638</v>
+        <v>509527</v>
       </c>
       <c r="R28" t="n">
-        <v>6983022</v>
+        <v>6983000</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3734,7 +3801,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118388830</v>
+        <v>118386677</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3767,29 +3834,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509546</v>
+        <v>509795</v>
       </c>
       <c r="R29" t="n">
-        <v>6982994</v>
+        <v>6982794</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3816,9 +3874,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3845,7 +3913,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118389380</v>
+        <v>118389609</v>
       </c>
       <c r="B30" t="n">
         <v>97853</v>
@@ -3880,12 +3948,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3894,13 +3957,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509533</v>
+        <v>509553</v>
       </c>
       <c r="R30" t="n">
-        <v>6983061</v>
+        <v>6983128</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3927,19 +3990,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,7 +4019,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118388342</v>
+        <v>118388600</v>
       </c>
       <c r="B31" t="n">
         <v>97853</v>
@@ -4001,7 +4054,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4015,10 +4068,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509663</v>
+        <v>509628</v>
       </c>
       <c r="R31" t="n">
-        <v>6983023</v>
+        <v>6983055</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4087,7 +4140,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118386422</v>
+        <v>118388830</v>
       </c>
       <c r="B32" t="n">
         <v>97853</v>
@@ -4122,27 +4175,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509823</v>
+        <v>509546</v>
       </c>
       <c r="R32" t="n">
-        <v>6982819</v>
+        <v>6982994</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4169,19 +4222,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4208,7 +4251,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118386834</v>
+        <v>118389865</v>
       </c>
       <c r="B33" t="n">
         <v>97853</v>
@@ -4253,14 +4296,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509731</v>
+        <v>509614</v>
       </c>
       <c r="R33" t="n">
-        <v>6982806</v>
+        <v>6983107</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4329,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118387192</v>
+        <v>118388685</v>
       </c>
       <c r="B34" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4341,47 +4384,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509740</v>
+        <v>509659</v>
       </c>
       <c r="R34" t="n">
-        <v>6982890</v>
+        <v>6983042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4450,10 +4484,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118388080</v>
+        <v>118389872</v>
       </c>
       <c r="B35" t="n">
-        <v>97853</v>
+        <v>82270</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4462,50 +4496,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509631</v>
+        <v>509635</v>
       </c>
       <c r="R35" t="n">
-        <v>6982967</v>
+        <v>6983073</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4532,19 +4557,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,10 +4586,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118388301</v>
+        <v>118388690</v>
       </c>
       <c r="B36" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4583,47 +4598,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509633</v>
+        <v>509589</v>
       </c>
       <c r="R36" t="n">
-        <v>6982957</v>
+        <v>6982988</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4682,10 +4688,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118389591</v>
+        <v>118386731</v>
       </c>
       <c r="B37" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4694,47 +4700,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509579</v>
+        <v>509786</v>
       </c>
       <c r="R37" t="n">
-        <v>6983105</v>
+        <v>6982814</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4803,10 +4800,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118390002</v>
+        <v>118388205</v>
       </c>
       <c r="B38" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4815,38 +4812,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509633</v>
+        <v>509638</v>
       </c>
       <c r="R38" t="n">
-        <v>6983026</v>
+        <v>6983015</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4915,7 +4921,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118388600</v>
+        <v>118388666</v>
       </c>
       <c r="B39" t="n">
         <v>97853</v>
@@ -4950,7 +4956,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4964,10 +4970,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509628</v>
+        <v>509650</v>
       </c>
       <c r="R39" t="n">
-        <v>6983055</v>
+        <v>6983040</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5036,7 +5042,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118386677</v>
+        <v>118389611</v>
       </c>
       <c r="B40" t="n">
         <v>97853</v>
@@ -5069,17 +5075,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509795</v>
+        <v>509572</v>
       </c>
       <c r="R40" t="n">
-        <v>6982794</v>
+        <v>6983118</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5148,10 +5163,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118387633</v>
+        <v>118389789</v>
       </c>
       <c r="B41" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5160,38 +5175,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509689</v>
+        <v>509597</v>
       </c>
       <c r="R41" t="n">
-        <v>6982906</v>
+        <v>6983133</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5250,7 +5269,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118386659</v>
+        <v>118386834</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -5285,7 +5304,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5299,10 +5318,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509786</v>
+        <v>509731</v>
       </c>
       <c r="R42" t="n">
-        <v>6982829</v>
+        <v>6982806</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5371,7 +5390,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118388565</v>
+        <v>118388958</v>
       </c>
       <c r="B43" t="n">
         <v>97853</v>
@@ -5404,26 +5423,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509621</v>
+        <v>509542</v>
       </c>
       <c r="R43" t="n">
-        <v>6983031</v>
+        <v>6982999</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5492,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118387645</v>
+        <v>118389356</v>
       </c>
       <c r="B44" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5504,50 +5514,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
+          <t>Tavnäs (Tavnäs), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509724</v>
+        <v>509532</v>
       </c>
       <c r="R44" t="n">
-        <v>6982889</v>
+        <v>6983056</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,19 +5579,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5613,10 +5608,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118389356</v>
+        <v>118387421</v>
       </c>
       <c r="B45" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5625,45 +5620,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>509532</v>
+        <v>509760</v>
       </c>
       <c r="R45" t="n">
-        <v>6983056</v>
+        <v>6982916</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5690,9 +5690,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5719,7 +5729,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118389611</v>
+        <v>118388526</v>
       </c>
       <c r="B46" t="n">
         <v>97853</v>
@@ -5754,27 +5764,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>509572</v>
+        <v>509630</v>
       </c>
       <c r="R46" t="n">
-        <v>6983118</v>
+        <v>6982963</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5801,19 +5811,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>08:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,7 +5840,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118388802</v>
+        <v>118387645</v>
       </c>
       <c r="B47" t="n">
         <v>97853</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tavnäs (Tavnäs), Jmt</t>
+          <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>509577</v>
+        <v>509724</v>
       </c>
       <c r="R47" t="n">
-        <v>6983044</v>
+        <v>6982889</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118765144</v>
+        <v>118765097</v>
       </c>
       <c r="B48" t="n">
         <v>97853</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>509640</v>
+        <v>509641</v>
       </c>
       <c r="R48" t="n">
-        <v>6983034</v>
+        <v>6983060</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6077,10 +6077,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118766047</v>
+        <v>118765047</v>
       </c>
       <c r="B49" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6089,25 +6089,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6115,24 +6115,19 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>509608</v>
+        <v>509638</v>
       </c>
       <c r="R49" t="n">
-        <v>6982971</v>
+        <v>6983069</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6161,7 +6156,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6171,7 +6166,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,10 +6193,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118765047</v>
+        <v>118766047</v>
       </c>
       <c r="B50" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,25 +6205,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6236,19 +6231,24 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skrivarhägnen (Skrivarhägnen), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>509638</v>
+        <v>509608</v>
       </c>
       <c r="R50" t="n">
-        <v>6983069</v>
+        <v>6982971</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765097</v>
+        <v>118765144</v>
       </c>
       <c r="B51" t="n">
         <v>97853</v>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>509641</v>
+        <v>509640</v>
       </c>
       <c r="R51" t="n">
-        <v>6983060</v>
+        <v>6983034</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6428,6 +6428,127 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120120406</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skrivarhägnen, Skrivarhägnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>509824</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6982845</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -6433,7 +6433,7 @@
         <v>120120406</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 22507-2024 artfynd.xlsx
+++ b/artfynd/A 22507-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6549,6 +6549,108 @@
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120454246</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87423</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skrivarhägnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>509827</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6982801</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
